--- a/2026/随机分队结果.xlsx
+++ b/2026/随机分队结果.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>陈芷涵</t>
+          <t>符方聪</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>朱玺云</t>
+          <t>胡湛欣</t>
         </is>
       </c>
     </row>
